--- a/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="176">
   <si>
     <t xml:space="preserve">Ref(s)</t>
   </si>
@@ -292,25 +292,22 @@
     <t xml:space="preserve">U4</t>
   </si>
   <si>
-    <t xml:space="preserve">Rail-clamp reference — TLV431B (±0.5%); sets the VS trip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vref 1.24 V, ±0.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-23 (DBZ)</t>
+    <t xml:space="preserve">Comparator + 1.242 V ref, open-drain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV3011BIDBVR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT-23-6</t>
   </si>
   <si>
     <t xml:space="preserve">Texas Instruments</t>
   </si>
   <si>
-    <t xml:space="preserve">TLV431BCDBZR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B grade (tighter) for a predictable clamp. tlv431a-3.pdf is TI's combined A/B datasheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tlv431a-3.pdf</t>
+    <t xml:space="preserve">TLV3011B comparator (SOT-23-6). Corrected 2026-07-04 from the stale v2 TLV431B — high-Z inputs let the R7/R8 divider go to 6.81M/3.74M for a tighter, lower-drain clamp. Pinout: 1=V+ 2=REF 3=IN- 4=GND 5=OUT 6=IN+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tlv3011b.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Q1</t>
@@ -1368,22 +1365,22 @@
         <v>93</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>22</v>
@@ -1391,25 +1388,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>0.45</v>
@@ -1421,10 +1418,10 @@
         <v>19</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>22</v>
@@ -1432,16 +1429,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>53</v>
@@ -1450,13 +1447,13 @@
         <v>54</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>58</v>
@@ -1467,13 +1464,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>66</v>
@@ -1491,7 +1488,7 @@
         <v>19</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>58</v>
@@ -1502,16 +1499,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>53</v>
@@ -1520,13 +1517,13 @@
         <v>54</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>58</v>
@@ -1537,16 +1534,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>53</v>
@@ -1555,13 +1552,13 @@
         <v>72</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>75</v>
@@ -1572,16 +1569,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>53</v>
@@ -1590,13 +1587,13 @@
         <v>72</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>75</v>
@@ -1607,16 +1604,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>53</v>
@@ -1625,13 +1622,13 @@
         <v>72</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>75</v>
@@ -1642,16 +1639,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>53</v>
@@ -1660,13 +1657,13 @@
         <v>72</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>75</v>
@@ -1677,16 +1674,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>53</v>
@@ -1695,13 +1692,13 @@
         <v>72</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>75</v>
@@ -1712,16 +1709,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>53</v>
@@ -1730,13 +1727,13 @@
         <v>72</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>75</v>
@@ -1747,16 +1744,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>53</v>
@@ -1765,13 +1762,13 @@
         <v>72</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>75</v>
@@ -1782,25 +1779,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>0.05</v>
@@ -1820,25 +1817,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0.75</v>
@@ -1850,10 +1847,10 @@
         <v>19</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>22</v>
@@ -1861,16 +1858,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>53</v>
@@ -1879,13 +1876,13 @@
         <v>72</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>75</v>
@@ -1896,16 +1893,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>53</v>
@@ -1914,13 +1911,13 @@
         <v>54</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>58</v>
@@ -1931,25 +1928,25 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0.55</v>
@@ -1961,10 +1958,10 @@
         <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>22</v>
@@ -1972,16 +1969,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>53</v>
@@ -1990,13 +1987,13 @@
         <v>54</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>58</v>
@@ -2007,26 +2004,26 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I30" s="1" t="n">
         <f aca="false">SUM(I2:I29)</f>
-        <v>20.642</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="183">
   <si>
     <t xml:space="preserve">Ref(s)</t>
   </si>
@@ -487,6 +487,27 @@
     <t xml:space="preserve">v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
   </si>
   <si>
+    <t xml:space="preserve">C13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED-anode bulk — supplies the glow-PWM transient locally, keeps it off the shared VS rail (MCU/accel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7 µF, X5R, 10 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM155R61A475ME15D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475ME15D is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(format-derived — confirm)</t>
+  </si>
+  <si>
     <t xml:space="preserve">R13</t>
   </si>
   <si>
@@ -541,7 +562,7 @@
     <t xml:space="preserve">Placed-parts subtotal (per board)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOTE: PCBWay turnkey BOM — machine-placed, bottom side, 38 parts. Converted 0402 lines + U6/R14 have prices blanked pending quote.</t>
+    <t xml:space="preserve">NOTE: PCBWay turnkey BOM — machine-placed, bottom side, 39 parts. Converted 0402 lines + U6/R14 have prices blanked pending quote.</t>
   </si>
   <si>
     <t xml:space="preserve">Hand-soldered by customer, NOT on this BOM: SC1-SC4 (supercaps), PV1-PV2 (solar cells).</t>
@@ -902,7 +923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1908,60 +1929,51 @@
         <v>53</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>158</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>0.55</v>
+        <v>165</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>22</v>
@@ -1981,22 +1993,28 @@
         <v>169</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0.55</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>22</v>
@@ -2004,26 +2022,62 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <f aca="false">SUM(I2:I29)</f>
+        <v>174</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <f aca="false">SUM(I2:I30)</f>
         <v>23.022</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PointLED 2-SMD flat-lead, ~3.4×1.25 mm</t>
+          <t>SMD, 3.4x1.9 mm</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>GRM155 224 (0.22 µF) — verify</t>
+          <t>GRM155R71C224KA12D</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>GRM155R61A475ME15D</t>
+          <t>GRM155R61A475MEAAD</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475ME15D is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
+          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475MEAAD is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">

--- a/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
+++ b/PCB/solar-glow-drh-v3_0-BOM-assembly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRH v3.0 ASSEMBLY BOM (placed)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DRH v3.0 ASSEMBLY BOM (placed)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>10 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>GRM155R71C103KA01D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>1 µF, X5R, 10 V</t>
+          <t>4.7 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D</t>
+          <t>GRM155R61A475MEAAD</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC] [DNP -&gt; drop on regen]</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>100 kΩ, ±1%</t>
+          <t>1 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>RC0402FR-07100KL</t>
+          <t>RC0402FR-071ML</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
